--- a/reports/jobs_2026-09-01.xlsx
+++ b/reports/jobs_2026-09-01.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Errors" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$82</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -520,12 +520,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Arm India</t>
+          <t>Agoda India</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Graduate Program - Engineering Pathways</t>
+          <t>Security Engineer (Bangkok Based, Relocation Support) IT Operations Bangkok, Thailand</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -546,12 +546,12 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/job/austin/graduate-program-engineering-pathways/33099/100011168736</t>
+          <t>https://careersatagoda.com/job/7552542-security-engineer-bangkok-based-relocation-support/</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/</t>
+          <t>https://careersatagoda.com/</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -568,12 +568,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Intern Program - Engineering Pathways</t>
+          <t>Engineer- Memory Design</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -581,7 +581,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -589,7 +593,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/job/austin/intern-program-engineering-pathways/33099/100011168720</t>
+          <t>https://careers.arm.com/job/bengaluru/engineer-memory-design/33099/100019619280</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -606,17 +610,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>MongoDB India</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Software Engineer 3</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -624,7 +628,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -632,12 +640,12 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Texas/AI-Engineer_SR-45356-1</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=8167389</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://boards.greenhouse.io/mongodb</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -647,57 +655,61 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Agnikul Cosmos</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Careers Inquiries humancapital@agnikul.in</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Software (General)</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>mailto:%20humancapital@agnikul.in</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>https://agnikul.in/careers</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Paytm</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Intern - Admin and Operations</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Noida, Uttar Pradesh</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/paytm/eea11d47-b37b-444f-aed9-ffc972e4c321</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/paytm</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Agoda India</t>
+          <t>Agnikul Cosmos</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Chiang Mai 1 available jobs</t>
+          <t>Careers Inquiries humancapital@agnikul.in</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -710,11 +722,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Mumbai 0 available jobs Ok</t>
-        </is>
-      </c>
+      <c r="E6" s="4" t="inlineStr"/>
       <c r="F6" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -722,12 +730,12 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/chiang-mai/</t>
+          <t>mailto:%20humancapital@agnikul.in</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/</t>
+          <t>https://agnikul.in/careers</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
@@ -744,7 +752,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Dubai 0 available jobs</t>
+          <t>Chiang Mai 1 available jobs</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -769,7 +777,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/dubai/</t>
+          <t>https://careersatagoda.com/location/chiang-mai/</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -791,7 +799,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Mumbai 0 available jobs</t>
+          <t>Dubai 0 available jobs</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -816,7 +824,7 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/mumbai/</t>
+          <t>https://careersatagoda.com/location/dubai/</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -838,7 +846,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Shanghai 0 available jobs</t>
+          <t>Mumbai 0 available jobs</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -863,7 +871,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/shanghai/</t>
+          <t>https://careersatagoda.com/location/mumbai/</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -885,7 +893,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Engineering &amp; Technology</t>
+          <t>Shanghai 0 available jobs</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -898,7 +906,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr"/>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Mumbai 0 available jobs Ok</t>
+        </is>
+      </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -906,7 +918,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/department/technology/</t>
+          <t>https://careersatagoda.com/location/shanghai/</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -928,7 +940,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Mumbai jobs</t>
+          <t>Engineering &amp; Technology</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -941,11 +953,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>Mumbai jobs Yokohama jobs</t>
-        </is>
-      </c>
+      <c r="E11" s="4" t="inlineStr"/>
       <c r="F11" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -953,7 +961,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/mumbai-india/</t>
+          <t>https://careersatagoda.com/department/technology/</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -975,12 +983,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Backend Developer Jobs</t>
+          <t>Mumbai jobs</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -988,7 +996,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr"/>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Mumbai jobs Yokohama jobs</t>
+        </is>
+      </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -996,7 +1008,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/vacancies/?search=back%20end</t>
+          <t>https://careersatagoda.com/location/mumbai-india/</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1018,12 +1030,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Developer Jobs</t>
+          <t>Backend Developer Jobs</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1039,7 +1051,7 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/vacancies/?search=Full%20Stack</t>
+          <t>https://careersatagoda.com/vacancies/?search=back%20end</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1061,12 +1073,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer Jobs</t>
+          <t>Full Stack Developer Jobs</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1082,7 +1094,7 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/vacancies/?search=software%20engineer</t>
+          <t>https://careersatagoda.com/vacancies/?search=Full%20Stack</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1099,12 +1111,12 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Arm India</t>
+          <t>Agoda India</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Theorem Proving Engineer</t>
+          <t>Software Engineer Jobs</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1125,12 +1137,12 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/job/austin/theorem-proving-engineer/33099/97584421536</t>
+          <t>https://careersatagoda.com/vacancies/?search=software%20engineer</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/</t>
+          <t>https://careersatagoda.com/</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -1369,17 +1381,17 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Fi Money</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Ai Engg Intern</t>
+          <t>Implementation Engineer</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -1389,7 +1401,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Gurgaon Full-time</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -1399,12 +1411,12 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/08c743e8-2b29-4f78-827e-5bd90476ed86</t>
+          <t>https://exotel.com/about-us/careers/#op-689879-implementation-engineer-</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
@@ -1416,17 +1428,17 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Fi Money</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>DS/ML Intern</t>
+          <t>Integration &amp; Customisation Engineer (PHP + React.JS)</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1436,7 +1448,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>India Full-time</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -1446,12 +1458,12 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/08fc1577-4593-4b94-b66b-08e638d29f37</t>
+          <t>https://exotel.com/about-us/careers/#op-703033-integration--customisation-engineer-php--reactjs</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
@@ -1463,17 +1475,17 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Fi Money</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>GenAI Product Builder Intern</t>
+          <t>Integration and Customisation Engineer - 2 (PHP+React.JS)</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1481,11 +1493,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
+      <c r="E23" s="4" t="inlineStr"/>
       <c r="F23" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -1493,12 +1501,12 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/4f5b7548-ea0a-4be0-816b-11d712853169</t>
+          <t>https://exotel.com/about-us/careers/#op-650435-integration-and-customisation-engineer-2-phpreactjs</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
@@ -1510,17 +1518,17 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>SharePoint Full Stack role</t>
+          <t>Product Support Intern (API Integration)</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1528,7 +1536,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr"/>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -1536,12 +1548,12 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Texas/SharePoint-Full-Stack-role_SR-42495-1</t>
+          <t>https://exotel.com/about-us/careers/#op-685404-product-support-intern-api-integration</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
@@ -1553,12 +1565,12 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>UI Developer - Digital Products</t>
+          <t>Implementation Engineer 2</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1571,7 +1583,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr"/>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru/ Gurgaon Full-time</t>
+        </is>
+      </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -1579,12 +1595,12 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Texas/UI-Developer---Digital-Products_SR-45168-1</t>
+          <t>https://exotel.com/about-us/careers/#op-705944-implementation-engineer-2</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
@@ -1596,17 +1612,17 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Freshworks</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Specialist - Data Platform Engineering</t>
+          <t>Software Engineer - 3 (Voice)</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>DevOps / SRE</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1616,7 +1632,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Chennai, in</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -1626,12 +1642,12 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/Freshworks/postings/744000143102264</t>
+          <t>https://exotel.com/about-us/careers/#op-704555-software-engineer-3-voice</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/Freshworks</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
@@ -1643,17 +1659,17 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Internships and Programs</t>
+          <t>Software Engineer 3 (Full Stack)</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1661,7 +1677,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr"/>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -1669,12 +1689,12 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
+          <t>https://exotel.com/about-us/careers/#op-697293-software-engineer-3-full-stack</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
@@ -1686,12 +1706,12 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
+          <t>Product Head, Voice AI</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1704,7 +1724,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr"/>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -1712,12 +1736,12 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
+          <t>https://exotel.com/about-us/careers/#op-705157-product-head-voice-ai</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
@@ -1729,12 +1753,12 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>HighRadius</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>Integration &amp; Customization Engineer -1</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1749,7 +1773,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>India Full-time</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -1759,12 +1783,12 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
+          <t>https://exotel.com/about-us/careers/#op-667737-integration--customization-engineer-1</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/highradius</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
@@ -1776,12 +1800,12 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Ixigo</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
+          <t>Forward Deployed Engineer - 2</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1796,7 +1820,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>New Delhi, in</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -1806,12 +1830,12 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
+          <t>https://exotel.com/about-us/careers/#op-705993-forward-deployed-engineer-2</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/ixigo</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
@@ -1823,17 +1847,17 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Ixigo</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (Agent Intelligence &amp; Evaluations)</t>
+          <t>Integration &amp; Customisation Engineer-1 (Chatbot)</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -1843,7 +1867,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>New Delhi, in</t>
+          <t>Bengaluru Full-time</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -1853,12 +1877,12 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000143976319</t>
+          <t>https://exotel.com/about-us/careers/#op-638792-integration--customisation-engineer1-chatbot</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/ixigo</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
@@ -1870,12 +1894,12 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Ixigo</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Software Engineer - 2 Backend</t>
+          <t>Software Developer - 3 (Golang/Java/Python)</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -1890,7 +1914,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Gurugram, in</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -1900,12 +1924,12 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000143738909</t>
+          <t>https://exotel.com/about-us/careers/#op-701453-software-developer-3-golangjavapython</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/ixigo</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
@@ -1917,17 +1941,17 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Lendingkart</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>Software Engineer - 2 (Voicebot)</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -1937,7 +1961,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru, in</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -1947,12 +1971,12 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
+          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/lendingkart</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
@@ -1964,17 +1988,17 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Licious</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>By: Licious DevOps</t>
+          <t>Software Engineer - 3 (Gen AI &amp; Speech)</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>DevOps / SRE</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -1982,7 +2006,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr"/>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore Full-time</t>
+        </is>
+      </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -1990,12 +2018,12 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>https://careers.licious.com/author/adminlic/</t>
+          <t>https://exotel.com/about-us/careers/#op-694350-software-engineer-3-gen-ai--speech</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>https://www.licious.in/careers</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
@@ -2007,17 +2035,17 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Internship Opportunities</t>
+          <t>Software Engineer 3 -Voice &amp; Messaging (Backend)</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -2025,7 +2053,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr"/>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -2033,12 +2065,12 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/pathways-programs/internships</t>
+          <t>https://exotel.com/about-us/careers/#op-701721-software-engineer-3-voice--messaging-backend</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
@@ -2050,17 +2082,17 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>Fi Money</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Ai Engg Intern</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -2068,7 +2100,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr"/>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -2076,12 +2112,12 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/Teams/Engineering</t>
+          <t>https://jobs.lever.co/epifi/08c743e8-2b29-4f78-827e-5bd90476ed86</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://jobs.lever.co/epifi</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
@@ -2093,17 +2129,17 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>MoEngage</t>
+          <t>Fi Money</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>For Developers</t>
+          <t>DS/ML Intern</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -2111,7 +2147,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr"/>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -2119,12 +2159,12 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/role/for-developers/</t>
+          <t>https://jobs.lever.co/epifi/08fc1577-4593-4b94-b66b-08e638d29f37</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/careers/</t>
+          <t>https://jobs.lever.co/epifi</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
@@ -2136,17 +2176,17 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Mphasis</t>
+          <t>Fi Money</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>TESTING</t>
+          <t>GenAI Product Builder Intern</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -2154,7 +2194,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr"/>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -2162,12 +2206,12 @@
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
+          <t>https://jobs.lever.co/epifi/4f5b7548-ea0a-4be0-816b-11d712853169</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/</t>
+          <t>https://jobs.lever.co/epifi</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
@@ -2179,17 +2223,17 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>PTC India</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Learn more about PTC internships</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -2205,12 +2249,12 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers/internships</t>
+          <t>https://fractal.ai/en-US/Careers/job/Texas/AI-Engineer_SR-45356-1</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
@@ -2222,17 +2266,17 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Intern-Talent Acquisition</t>
+          <t>SharePoint Full Stack role</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -2240,11 +2284,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore, Karnataka</t>
-        </is>
-      </c>
+      <c r="E40" s="4" t="inlineStr"/>
       <c r="F40" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -2252,12 +2292,12 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
+          <t>https://fractal.ai/en-US/Careers/job/Texas/SharePoint-Full-Stack-role_SR-42495-1</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
@@ -2269,17 +2309,17 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Product Management - Intern - Telco.</t>
+          <t>UI Developer - Digital Products</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -2287,11 +2327,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>Noida, Uttar Pradesh</t>
-        </is>
-      </c>
+      <c r="E41" s="4" t="inlineStr"/>
       <c r="F41" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -2299,12 +2335,12 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/5648edd6-b73b-4156-96f5-343f4d851610</t>
+          <t>https://fractal.ai/en-US/Careers/job/Texas/UI-Developer---Digital-Products_SR-45168-1</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
@@ -2316,27 +2352,27 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Freshworks</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Product Management Intern- Insurance</t>
+          <t>Specialist - Data Platform Engineering</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>DevOps / SRE</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>recent graduate</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh</t>
+          <t>Chennai, in</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -2346,12 +2382,12 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/4a97658f-ac6f-4a86-b483-ae50dd5c7a46</t>
+          <t>https://api.smartrecruiters.com/v1/companies/Freshworks/postings/744000143102264</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://careers.smartrecruiters.com/Freshworks</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
@@ -2363,12 +2399,12 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern</t>
+          <t>Internships and Programs</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -2381,11 +2417,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>Noida, Uttar Pradesh</t>
-        </is>
-      </c>
+      <c r="E43" s="4" t="inlineStr"/>
       <c r="F43" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -2393,12 +2425,12 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/08ee2a10-3268-497e-bc10-7c7fee7caa66</t>
+          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
@@ -2410,12 +2442,12 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Publicis Sapient India</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Join our engineering talent community</t>
+          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -2436,12 +2468,12 @@
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
+          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>https://careers.publicissapient.com/</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
@@ -2453,17 +2485,17 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>HighRadius</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -2473,7 +2505,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Indore, in</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -2483,12 +2515,12 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
+          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://boards.greenhouse.io/highradius</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
@@ -2500,12 +2532,12 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Ixigo</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Laravel Developer</t>
+          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -2520,7 +2552,7 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Indore, in</t>
+          <t>New Delhi, in</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -2530,12 +2562,12 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://careers.smartrecruiters.com/ixigo</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
@@ -2547,17 +2579,17 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Ixigo</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Node.js Developer</t>
+          <t>Machine Learning Engineer (Agent Intelligence &amp; Evaluations)</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -2567,7 +2599,7 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Indore, in</t>
+          <t>New Delhi, in</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -2577,12 +2609,12 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000143976319</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://careers.smartrecruiters.com/ixigo</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
@@ -2594,17 +2626,17 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>Ramco Systems</t>
+          <t>Ixigo</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Internships</t>
+          <t xml:space="preserve"> Software Engineer - 2 Backend</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -2612,7 +2644,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr"/>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram, in</t>
+        </is>
+      </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -2620,12 +2656,12 @@
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000143738909</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/</t>
+          <t>https://careers.smartrecruiters.com/ixigo</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
@@ -2637,17 +2673,17 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Razorpay</t>
+          <t>Lendingkart</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -2657,7 +2693,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bengaluru, in</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -2667,12 +2703,12 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4723067005</t>
+          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/razorpaysoftwareprivatelimited</t>
+          <t>https://careers.smartrecruiters.com/lendingkart</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
@@ -2684,17 +2720,17 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Razorpay</t>
+          <t>Licious</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Builder</t>
+          <t>By: Licious DevOps</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>DevOps / SRE</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -2702,11 +2738,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E50" s="4" t="inlineStr"/>
       <c r="F50" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -2714,12 +2746,12 @@
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4699107005</t>
+          <t>https://careers.licious.com/author/adminlic/</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/razorpaysoftwareprivatelimited</t>
+          <t>https://www.licious.in/careers</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
@@ -2731,17 +2763,17 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Payroll Industrial Trainee</t>
+          <t>Internship Opportunities</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -2749,11 +2781,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
+      <c r="E51" s="4" t="inlineStr"/>
       <c r="F51" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -2761,12 +2789,12 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8070886?gh_jid=8070886</t>
+          <t>https://careers.linkedin.com/pathways-programs/internships</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
@@ -2778,12 +2806,12 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - IAM</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -2796,11 +2824,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>Pune</t>
-        </is>
-      </c>
+      <c r="E52" s="4" t="inlineStr"/>
       <c r="F52" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -2808,12 +2832,12 @@
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
+          <t>https://careers.linkedin.com/Teams/Engineering</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
@@ -2825,17 +2849,17 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Sarvam AI</t>
+          <t>MoEngage</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Product Operations &amp; Analytics Intern</t>
+          <t>For Developers</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -2843,11 +2867,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E53" s="4" t="inlineStr"/>
       <c r="F53" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -2855,12 +2875,12 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/sarvam/6a5df2a7-5335-41b7-9b50-7f2f5de26d18</t>
+          <t>https://www.moengage.com/role/for-developers/</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/sarvam</t>
+          <t>https://www.moengage.com/careers/</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
@@ -2872,17 +2892,17 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Scaler</t>
+          <t>Mphasis</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
+          <t>TESTING</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -2890,11 +2910,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>Remote Instructor- Python</t>
-        </is>
-      </c>
+      <c r="E54" s="4" t="inlineStr"/>
       <c r="F54" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -2902,12 +2918,12 @@
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/remote-instructor-python</t>
+          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/</t>
+          <t>https://careers.mphasis.com/</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
@@ -2919,12 +2935,12 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>PTC India</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Intern - Content Moderation (Hindi &amp; Punjabi)</t>
+          <t>Learn more about PTC internships</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -2945,12 +2961,12 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MjksInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://www.ptc.com/en/careers/internships</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://www.ptc.com/en/careers</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
@@ -2962,17 +2978,17 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>AI Animator</t>
+          <t>Intern-Talent Acquisition</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -2980,7 +2996,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr"/>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -2988,12 +3008,12 @@
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MTYsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
@@ -3005,17 +3025,17 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>AI Animator</t>
+          <t>Product Management - Intern - Telco.</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -3023,7 +3043,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr"/>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>Noida, Uttar Pradesh</t>
+        </is>
+      </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -3031,12 +3055,12 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MTEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://jobs.lever.co/paytm/5648edd6-b73b-4156-96f5-343f4d851610</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
@@ -3048,25 +3072,29 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Video Editor- AI</t>
+          <t>Product Management Intern- Insurance</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="inlineStr"/>
+          <t>recent graduate</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>Noida, Uttar Pradesh</t>
+        </is>
+      </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -3074,12 +3102,12 @@
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjIzOTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://jobs.lever.co/paytm/4a97658f-ac6f-4a86-b483-ae50dd5c7a46</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
@@ -3091,17 +3119,17 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>QA Engineer</t>
+          <t>Talent Acquisition Intern</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -3111,7 +3139,7 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Gurugram, in</t>
+          <t>Noida, Uttar Pradesh</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
@@ -3121,12 +3149,12 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
+          <t>https://jobs.lever.co/paytm/08ee2a10-3268-497e-bc10-7c7fee7caa66</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
@@ -3138,17 +3166,17 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>Publicis Sapient India</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
+          <t>Join our engineering talent community</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -3156,11 +3184,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram, in</t>
-        </is>
-      </c>
+      <c r="E60" s="4" t="inlineStr"/>
       <c r="F60" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -3168,12 +3192,12 @@
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
+          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
+          <t>https://careers.publicissapient.com/</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
@@ -3185,17 +3209,17 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Snowflake India</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Account Engineer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -3205,7 +3229,7 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>CO-Colombia-Remote</t>
+          <t>Indore, in</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -3215,12 +3239,12 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/snowflake/4fafd350-a140-426f-8602-310b8d75b5fd</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/snowflake</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
@@ -3232,17 +3256,17 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Sprinklr</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Internship and Early Careers</t>
+          <t>Laravel Developer</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -3250,7 +3274,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr"/>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>Indore, in</t>
+        </is>
+      </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -3258,12 +3286,12 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr">
@@ -3275,17 +3303,17 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Stripe India</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Intern</t>
+          <t>Node.js Developer</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -3295,7 +3323,7 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Indore, in</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -3305,12 +3333,12 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/stripe</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
@@ -3322,17 +3350,17 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Unacademy</t>
+          <t>Ramco Systems</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Test Jerin</t>
+          <t>Internships</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -3340,11 +3368,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru, in</t>
-        </is>
-      </c>
+      <c r="E64" s="4" t="inlineStr"/>
       <c r="F64" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -3352,12 +3376,12 @@
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
+          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/unacademy</t>
+          <t>https://www.ramco.com/careers/</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
@@ -3369,17 +3393,17 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Unacademy</t>
+          <t>Razorpay</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -3389,7 +3413,7 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru, in</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -3399,12 +3423,12 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
+          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4723067005</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/unacademy</t>
+          <t>https://boards.greenhouse.io/razorpaysoftwareprivatelimited</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
@@ -3416,27 +3440,27 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Zscaler India</t>
+          <t>Razorpay</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Full Stack Builder</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>1 - 3 years</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Bangalore, IND</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -3446,12 +3470,12 @@
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/zscaler/jobs/5219488007</t>
+          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4699107005</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/zscaler</t>
+          <t>https://boards.greenhouse.io/razorpaysoftwareprivatelimited</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
@@ -3463,12 +3487,12 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>upGrad</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Data Science Bootcamp with AI</t>
+          <t>Payroll Industrial Trainee</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -3481,7 +3505,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr"/>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -3489,12 +3517,12 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>https://www.upgrad.com/bootcamps/job-linked-data-science-advanced-bootcamp/</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8070886?gh_jid=8070886</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>https://www.upgrad.com/careers/</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
@@ -3503,8 +3531,693 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>Rubrik India</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer - IAM</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/rubrik</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>Sarvam AI</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>Product Operations &amp; Analytics Intern</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/sarvam/6a5df2a7-5335-41b7-9b50-7f2f5de26d18</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/sarvam</t>
+        </is>
+      </c>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>Scaler</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>Remote Instructor- Python</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/careers/remote-instructor-python</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/careers/</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>ShareChat</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>Intern - Content Moderation (Hindi &amp; Punjabi)</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr"/>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MjksInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>https://sharechat.com/careers</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>ShareChat</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>AI Animator</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr"/>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MTYsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>https://sharechat.com/careers</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>ShareChat</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>AI Animator</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr"/>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MTEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>https://sharechat.com/careers</t>
+        </is>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>ShareChat</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>Video Editor- AI</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr"/>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjIzOTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>https://sharechat.com/careers</t>
+        </is>
+      </c>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>Shipsy</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>QA Engineer</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>QA / SDET</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram, in</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
+        </is>
+      </c>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>Shipsy</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>Full Stack</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram, in</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
+        </is>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>Snowflake India</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>Account Engineer</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>CO-Colombia-Remote</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/snowflake/4fafd350-a140-426f-8602-310b8d75b5fd</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/snowflake</t>
+        </is>
+      </c>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>Sprinklr</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>Internship and Early Careers</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr"/>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sprinklr.com/careers/</t>
+        </is>
+      </c>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>Stripe India</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer, Intern</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/stripe</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>Unacademy</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>Test Jerin</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.smartrecruiters.com/unacademy</t>
+        </is>
+      </c>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>Unacademy</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer, Backend</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.smartrecruiters.com/unacademy</t>
+        </is>
+      </c>
+      <c r="I81" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>Zscaler India</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>1 - 3 years</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore, IND</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/zscaler/jobs/5219488007</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/zscaler</t>
+        </is>
+      </c>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I67"/>
+  <autoFilter ref="A1:I82"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -3572,6 +4285,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId81"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3611,35 +4339,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Cuemath</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://www.cuemath.com/careers/</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://exotel.com/careers/", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Cuemath</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>https://www.cuemath.com/careers/</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -3648,18 +4356,18 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Log9 Materials</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>https://www.log9materials.com/careers</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -3668,18 +4376,18 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Signzy</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>https://www.signzy.com/careers/</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -3688,18 +4396,18 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Ather Energy</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>https://www.atherenergy.com/careers</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -3708,18 +4416,18 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Nykaa</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>https://www.nykaa.com/careers</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.nykaa.com/careers
 Call log:
@@ -3728,18 +4436,18 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Juspay</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>https://juspay.io/careers</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -3748,18 +4456,18 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>MakeMyTrip</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>https://careers.makemytrip.com/</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -3768,6 +4476,26 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FirstCry</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>https://www.firstcry.com/careers</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.firstcry.com/careers", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
@@ -3811,35 +4539,15 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Tata 1mg</t>
+          <t>Coforge</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://www.1mg.com/jobs</t>
+          <t>https://www.coforge.com/careers</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.1mg.com/jobs", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Coforge</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>https://www.coforge.com/careers</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.coforge.com/careers
 Call log:
@@ -3848,18 +4556,18 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Persistent Systems</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>https://www.persistent.com/careers/</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.persistent.com/careers/
 Call log:
@@ -3868,6 +4576,26 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>upGrad</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>https://www.upgrad.com/careers/</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.upgrad.com/careers/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
